--- a/outputs/historico_simulaciones.xlsx
+++ b/outputs/historico_simulaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -660,6 +660,165 @@
       </c>
       <c r="Q4" t="n">
         <v>7812.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>160</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>450</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9200</v>
+      </c>
+      <c r="E5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>900000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1940000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.8818181818181818</v>
+      </c>
+      <c r="O5" t="n">
+        <v>290</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3103.448275862069</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4888.888888888889</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>160</v>
+      </c>
+      <c r="B6" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>450</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9200</v>
+      </c>
+      <c r="E6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>900000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1940000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.8818181818181818</v>
+      </c>
+      <c r="O6" t="n">
+        <v>290</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3103.448275862069</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4888.888888888889</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>160</v>
+      </c>
+      <c r="B7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>450</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9200</v>
+      </c>
+      <c r="E7" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>900000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1940000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8818181818181818</v>
+      </c>
+      <c r="O7" t="n">
+        <v>290</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3103.448275862069</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4888.888888888889</v>
       </c>
     </row>
   </sheetData>
